--- a/bookgit.xlsx
+++ b/bookgit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0aecc089ecbfcae/Desktop/New folder (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCC0CB37-D8E9-47F8-A2D3-076DA950041F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{BCC0CB37-D8E9-47F8-A2D3-076DA950041F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C40E5F6-A6E5-46A1-ADE7-8002AD5774A3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C3EFE19F-F6A9-4AEF-BE4E-4F7E94C0A578}"/>
   </bookViews>
@@ -380,9 +380,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4255B2EA-0113-44E6-94DF-5381AB228A97}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>